--- a/docs/workbook-split/dateien/System.xlsx
+++ b/docs/workbook-split/dateien/System.xlsx
@@ -2208,6 +2208,8 @@
       <c r="F115" s="9" t="n"/>
       <c r="G115" s="9" t="n"/>
     </row>
+    <row r="116"/>
+    <row r="117"/>
     <row r="118">
       <c r="C118" t="inlineStr">
         <is>
